--- a/总表（单双排改点后）.xlsx
+++ b/总表（单双排改点后）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\py_xw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28BE21A-4638-4E5D-A489-5CCB7EB387FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318FC894-2A92-42F2-B2C1-750A0BBDFB0C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="18525" windowHeight="7125" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16771,66 +16771,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -16857,30 +16797,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -16977,6 +16893,90 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -17413,49 +17413,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="135" t="s">
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="137"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="109"/>
     </row>
     <row r="2" spans="1:14" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="131"/>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="139"/>
-      <c r="L2" s="139"/>
-      <c r="M2" s="140"/>
+      <c r="A2" s="103"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="112"/>
     </row>
     <row r="3" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="133"/>
-      <c r="B3" s="133"/>
-      <c r="C3" s="133"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="133"/>
-      <c r="I3" s="134"/>
+      <c r="A3" s="105"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="106"/>
       <c r="J3" s="12" t="s">
         <v>2</v>
       </c>
@@ -17470,72 +17470,72 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="141" t="s">
+      <c r="A4" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="142"/>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="142"/>
-      <c r="H4" s="142"/>
-      <c r="I4" s="142"/>
-      <c r="J4" s="145" t="s">
+      <c r="B4" s="114"/>
+      <c r="C4" s="114"/>
+      <c r="D4" s="114"/>
+      <c r="E4" s="114"/>
+      <c r="F4" s="114"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="128">
+      <c r="K4" s="100">
         <v>20</v>
       </c>
-      <c r="L4" s="129">
+      <c r="L4" s="101">
         <v>2903939382</v>
       </c>
-      <c r="M4" s="130" t="s">
+      <c r="M4" s="102" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="143"/>
-      <c r="B5" s="144"/>
-      <c r="C5" s="144"/>
-      <c r="D5" s="144"/>
-      <c r="E5" s="144"/>
-      <c r="F5" s="144"/>
-      <c r="G5" s="144"/>
-      <c r="H5" s="144"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="145"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="129"/>
-      <c r="M5" s="130"/>
+      <c r="A5" s="115"/>
+      <c r="B5" s="116"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116"/>
+      <c r="I5" s="116"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="101"/>
+      <c r="M5" s="102"/>
     </row>
     <row r="6" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="143"/>
-      <c r="B6" s="144"/>
-      <c r="C6" s="144"/>
-      <c r="D6" s="144"/>
-      <c r="E6" s="144"/>
-      <c r="F6" s="144"/>
-      <c r="G6" s="144"/>
-      <c r="H6" s="144"/>
-      <c r="I6" s="144"/>
-      <c r="J6" s="145"/>
-      <c r="K6" s="128"/>
-      <c r="L6" s="129"/>
-      <c r="M6" s="130"/>
+      <c r="A6" s="115"/>
+      <c r="B6" s="116"/>
+      <c r="C6" s="116"/>
+      <c r="D6" s="116"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="116"/>
+      <c r="G6" s="116"/>
+      <c r="H6" s="116"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="101"/>
+      <c r="M6" s="102"/>
     </row>
     <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="91" t="s">
+      <c r="A7" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="93"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="150"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="151"/>
       <c r="J7" s="16" t="s">
         <v>10</v>
       </c>
@@ -17551,17 +17551,17 @@
       <c r="N7" s="20"/>
     </row>
     <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="146" t="s">
+      <c r="A8" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="147"/>
-      <c r="C8" s="147"/>
-      <c r="D8" s="147"/>
-      <c r="E8" s="147"/>
-      <c r="F8" s="147"/>
-      <c r="G8" s="147"/>
-      <c r="H8" s="147"/>
-      <c r="I8" s="148"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="120"/>
       <c r="J8" s="21" t="s">
         <v>13</v>
       </c>
@@ -17577,15 +17577,15 @@
       <c r="N8" s="2"/>
     </row>
     <row r="9" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="146"/>
-      <c r="B9" s="147"/>
-      <c r="C9" s="147"/>
-      <c r="D9" s="147"/>
-      <c r="E9" s="147"/>
-      <c r="F9" s="147"/>
-      <c r="G9" s="147"/>
-      <c r="H9" s="147"/>
-      <c r="I9" s="148"/>
+      <c r="A9" s="118"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="120"/>
       <c r="J9" s="25" t="s">
         <v>16</v>
       </c>
@@ -17601,15 +17601,15 @@
       <c r="N9" s="2"/>
     </row>
     <row r="10" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="146"/>
-      <c r="B10" s="147"/>
-      <c r="C10" s="147"/>
-      <c r="D10" s="147"/>
-      <c r="E10" s="147"/>
-      <c r="F10" s="147"/>
-      <c r="G10" s="147"/>
-      <c r="H10" s="147"/>
-      <c r="I10" s="148"/>
+      <c r="A10" s="118"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="120"/>
       <c r="J10" s="29" t="s">
         <v>18</v>
       </c>
@@ -17625,15 +17625,15 @@
       <c r="N10" s="2"/>
     </row>
     <row r="11" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="146"/>
-      <c r="B11" s="147"/>
-      <c r="C11" s="147"/>
-      <c r="D11" s="147"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="147"/>
-      <c r="G11" s="147"/>
-      <c r="H11" s="147"/>
-      <c r="I11" s="148"/>
+      <c r="A11" s="118"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="120"/>
       <c r="J11" s="25" t="s">
         <v>20</v>
       </c>
@@ -17649,15 +17649,15 @@
       <c r="N11" s="2"/>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="149"/>
-      <c r="B12" s="150"/>
-      <c r="C12" s="150"/>
-      <c r="D12" s="150"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="150"/>
-      <c r="G12" s="150"/>
-      <c r="H12" s="150"/>
-      <c r="I12" s="151"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="123"/>
       <c r="J12" s="33" t="s">
         <v>22</v>
       </c>
@@ -17673,17 +17673,17 @@
       <c r="N12" s="2"/>
     </row>
     <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="94" t="s">
+      <c r="A13" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="95"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
+      <c r="B13" s="153"/>
+      <c r="C13" s="153"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="153"/>
+      <c r="H13" s="153"/>
+      <c r="I13" s="153"/>
       <c r="J13" s="37" t="s">
         <v>25</v>
       </c>
@@ -17702,18 +17702,18 @@
       <c r="A14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="96" t="s">
+      <c r="B14" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="97" t="s">
+      <c r="C14" s="154"/>
+      <c r="D14" s="154"/>
+      <c r="E14" s="154"/>
+      <c r="F14" s="155" t="s">
         <v>29</v>
       </c>
-      <c r="G14" s="97"/>
-      <c r="H14" s="97"/>
-      <c r="I14" s="98"/>
+      <c r="G14" s="155"/>
+      <c r="H14" s="155"/>
+      <c r="I14" s="156"/>
       <c r="J14" s="38" t="s">
         <v>30</v>
       </c>
@@ -17732,18 +17732,18 @@
       <c r="A15" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="99" t="s">
+      <c r="B15" s="157" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="99"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="100" t="s">
+      <c r="C15" s="157"/>
+      <c r="D15" s="157"/>
+      <c r="E15" s="157"/>
+      <c r="F15" s="158" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="100"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="101"/>
+      <c r="G15" s="158"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="159"/>
       <c r="J15" s="42" t="s">
         <v>35</v>
       </c>
@@ -17761,18 +17761,18 @@
       <c r="A16" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="102"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="102"/>
-      <c r="F16" s="103" t="s">
+      <c r="C16" s="142"/>
+      <c r="D16" s="142"/>
+      <c r="E16" s="142"/>
+      <c r="F16" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="104"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="144"/>
       <c r="J16" s="44" t="s">
         <v>40</v>
       </c>
@@ -17790,18 +17790,18 @@
       <c r="A17" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="105" t="s">
+      <c r="B17" s="145" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="105"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="105"/>
-      <c r="F17" s="103" t="s">
+      <c r="C17" s="145"/>
+      <c r="D17" s="145"/>
+      <c r="E17" s="145"/>
+      <c r="F17" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="104"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="143"/>
+      <c r="I17" s="144"/>
       <c r="J17" s="44" t="s">
         <v>44</v>
       </c>
@@ -17819,18 +17819,18 @@
       <c r="A18" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="106" t="s">
+      <c r="B18" s="146" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="106"/>
-      <c r="D18" s="106"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="107" t="s">
+      <c r="C18" s="146"/>
+      <c r="D18" s="146"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="147" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="107"/>
-      <c r="H18" s="107"/>
-      <c r="I18" s="108"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="147"/>
+      <c r="I18" s="148"/>
       <c r="J18" s="44" t="s">
         <v>48</v>
       </c>
@@ -17848,18 +17848,18 @@
       <c r="A19" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="120" t="s">
+      <c r="B19" s="134" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="120"/>
-      <c r="D19" s="120"/>
-      <c r="E19" s="120"/>
-      <c r="F19" s="121" t="s">
+      <c r="C19" s="134"/>
+      <c r="D19" s="134"/>
+      <c r="E19" s="134"/>
+      <c r="F19" s="135" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="121"/>
-      <c r="H19" s="121"/>
-      <c r="I19" s="122"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="136"/>
       <c r="J19" s="44" t="s">
         <v>53</v>
       </c>
@@ -17875,18 +17875,18 @@
       <c r="A20" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="123" t="s">
+      <c r="B20" s="137" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="123"/>
-      <c r="D20" s="123"/>
-      <c r="E20" s="123"/>
-      <c r="F20" s="124" t="s">
+      <c r="C20" s="137"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="138" t="s">
         <v>56</v>
       </c>
-      <c r="G20" s="124"/>
-      <c r="H20" s="124"/>
-      <c r="I20" s="124"/>
+      <c r="G20" s="138"/>
+      <c r="H20" s="138"/>
+      <c r="I20" s="138"/>
       <c r="J20" s="49" t="s">
         <v>57</v>
       </c>
@@ -17899,323 +17899,323 @@
       <c r="M20" s="52"/>
     </row>
     <row r="21" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="125" t="s">
+      <c r="A21" s="139" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="126"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="126"/>
-      <c r="H21" s="126"/>
-      <c r="I21" s="127"/>
+      <c r="B21" s="140"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="140"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="141"/>
     </row>
     <row r="22" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="152" t="s">
+      <c r="A22" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="153"/>
-      <c r="C22" s="153"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="153"/>
-      <c r="G22" s="153"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="154"/>
+      <c r="B22" s="125"/>
+      <c r="C22" s="125"/>
+      <c r="D22" s="125"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="125"/>
+      <c r="I22" s="126"/>
     </row>
     <row r="23" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="155"/>
-      <c r="B23" s="156"/>
-      <c r="C23" s="156"/>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
-      <c r="F23" s="156"/>
-      <c r="G23" s="156"/>
-      <c r="H23" s="156"/>
-      <c r="I23" s="157"/>
+      <c r="A23" s="127"/>
+      <c r="B23" s="128"/>
+      <c r="C23" s="128"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="129"/>
     </row>
     <row r="24" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="158" t="s">
+      <c r="A24" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="159"/>
-      <c r="C24" s="159"/>
-      <c r="D24" s="159"/>
-      <c r="E24" s="159"/>
-      <c r="F24" s="159"/>
-      <c r="G24" s="159"/>
-      <c r="H24" s="159"/>
-      <c r="I24" s="159"/>
+      <c r="B24" s="131"/>
+      <c r="C24" s="131"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="131"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="131"/>
+      <c r="I24" s="131"/>
     </row>
     <row r="25" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="159"/>
-      <c r="B25" s="159"/>
-      <c r="C25" s="159"/>
-      <c r="D25" s="159"/>
-      <c r="E25" s="159"/>
-      <c r="F25" s="159"/>
-      <c r="G25" s="159"/>
-      <c r="H25" s="159"/>
-      <c r="I25" s="159"/>
+      <c r="A25" s="131"/>
+      <c r="B25" s="131"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="131"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="131"/>
+      <c r="I25" s="131"/>
     </row>
     <row r="26" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="159"/>
-      <c r="B26" s="159"/>
-      <c r="C26" s="159"/>
-      <c r="D26" s="159"/>
-      <c r="E26" s="159"/>
-      <c r="F26" s="159"/>
-      <c r="G26" s="159"/>
-      <c r="H26" s="159"/>
-      <c r="I26" s="159"/>
+      <c r="A26" s="131"/>
+      <c r="B26" s="131"/>
+      <c r="C26" s="131"/>
+      <c r="D26" s="131"/>
+      <c r="E26" s="131"/>
+      <c r="F26" s="131"/>
+      <c r="G26" s="131"/>
+      <c r="H26" s="131"/>
+      <c r="I26" s="131"/>
     </row>
     <row r="27" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="159"/>
-      <c r="B27" s="159"/>
-      <c r="C27" s="159"/>
-      <c r="D27" s="159"/>
-      <c r="E27" s="159"/>
-      <c r="F27" s="159"/>
-      <c r="G27" s="159"/>
-      <c r="H27" s="159"/>
-      <c r="I27" s="159"/>
+      <c r="A27" s="131"/>
+      <c r="B27" s="131"/>
+      <c r="C27" s="131"/>
+      <c r="D27" s="131"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="131"/>
+      <c r="I27" s="131"/>
     </row>
     <row r="28" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="159"/>
-      <c r="B28" s="159"/>
-      <c r="C28" s="159"/>
-      <c r="D28" s="159"/>
-      <c r="E28" s="159"/>
-      <c r="F28" s="159"/>
-      <c r="G28" s="159"/>
-      <c r="H28" s="159"/>
-      <c r="I28" s="159"/>
+      <c r="A28" s="131"/>
+      <c r="B28" s="131"/>
+      <c r="C28" s="131"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="131"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="131"/>
+      <c r="I28" s="131"/>
     </row>
     <row r="29" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="159"/>
-      <c r="B29" s="159"/>
-      <c r="C29" s="159"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="159"/>
-      <c r="F29" s="159"/>
-      <c r="G29" s="159"/>
-      <c r="H29" s="159"/>
-      <c r="I29" s="159"/>
+      <c r="A29" s="131"/>
+      <c r="B29" s="131"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="131"/>
     </row>
     <row r="30" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="159"/>
-      <c r="B30" s="159"/>
-      <c r="C30" s="159"/>
-      <c r="D30" s="159"/>
-      <c r="E30" s="159"/>
-      <c r="F30" s="159"/>
-      <c r="G30" s="159"/>
-      <c r="H30" s="159"/>
-      <c r="I30" s="159"/>
+      <c r="A30" s="131"/>
+      <c r="B30" s="131"/>
+      <c r="C30" s="131"/>
+      <c r="D30" s="131"/>
+      <c r="E30" s="131"/>
+      <c r="F30" s="131"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="131"/>
+      <c r="I30" s="131"/>
     </row>
     <row r="31" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="159"/>
-      <c r="B31" s="159"/>
-      <c r="C31" s="159"/>
-      <c r="D31" s="159"/>
-      <c r="E31" s="159"/>
-      <c r="F31" s="159"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="159"/>
-      <c r="I31" s="159"/>
+      <c r="A31" s="131"/>
+      <c r="B31" s="131"/>
+      <c r="C31" s="131"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="131"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="131"/>
     </row>
     <row r="32" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="133" t="s">
+      <c r="A32" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="133"/>
-      <c r="C32" s="133"/>
-      <c r="D32" s="133"/>
-      <c r="E32" s="133"/>
-      <c r="F32" s="133"/>
-      <c r="G32" s="133"/>
-      <c r="H32" s="133"/>
-      <c r="I32" s="133"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="105"/>
     </row>
     <row r="33" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="109" t="s">
+      <c r="A33" s="132" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="109"/>
-      <c r="C33" s="109"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="109"/>
-      <c r="H33" s="109"/>
-      <c r="I33" s="109"/>
+      <c r="B33" s="132"/>
+      <c r="C33" s="132"/>
+      <c r="D33" s="132"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="132"/>
+      <c r="H33" s="132"/>
+      <c r="I33" s="132"/>
     </row>
     <row r="34" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="109"/>
-      <c r="B34" s="109"/>
-      <c r="C34" s="109"/>
-      <c r="D34" s="109"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="109"/>
-      <c r="G34" s="109"/>
-      <c r="H34" s="109"/>
-      <c r="I34" s="109"/>
+      <c r="A34" s="132"/>
+      <c r="B34" s="132"/>
+      <c r="C34" s="132"/>
+      <c r="D34" s="132"/>
+      <c r="E34" s="132"/>
+      <c r="F34" s="132"/>
+      <c r="G34" s="132"/>
+      <c r="H34" s="132"/>
+      <c r="I34" s="132"/>
     </row>
     <row r="35" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="133" t="s">
+      <c r="A35" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="133"/>
-      <c r="C35" s="133"/>
-      <c r="D35" s="133"/>
-      <c r="E35" s="133"/>
-      <c r="F35" s="133"/>
-      <c r="G35" s="133"/>
-      <c r="H35" s="133"/>
-      <c r="I35" s="133"/>
+      <c r="B35" s="105"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="105"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="105"/>
+      <c r="H35" s="105"/>
+      <c r="I35" s="105"/>
     </row>
     <row r="36" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="132" t="s">
         <v>64</v>
       </c>
-      <c r="B36" s="109"/>
-      <c r="C36" s="109"/>
-      <c r="D36" s="109"/>
-      <c r="E36" s="109"/>
-      <c r="F36" s="109"/>
-      <c r="G36" s="109"/>
-      <c r="H36" s="109"/>
-      <c r="I36" s="109"/>
+      <c r="B36" s="132"/>
+      <c r="C36" s="132"/>
+      <c r="D36" s="132"/>
+      <c r="E36" s="132"/>
+      <c r="F36" s="132"/>
+      <c r="G36" s="132"/>
+      <c r="H36" s="132"/>
+      <c r="I36" s="132"/>
     </row>
     <row r="37" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="110"/>
-      <c r="B37" s="110"/>
-      <c r="C37" s="110"/>
-      <c r="D37" s="110"/>
-      <c r="E37" s="110"/>
-      <c r="F37" s="110"/>
-      <c r="G37" s="110"/>
-      <c r="H37" s="110"/>
-      <c r="I37" s="110"/>
+      <c r="A37" s="133"/>
+      <c r="B37" s="133"/>
+      <c r="C37" s="133"/>
+      <c r="D37" s="133"/>
+      <c r="E37" s="133"/>
+      <c r="F37" s="133"/>
+      <c r="G37" s="133"/>
+      <c r="H37" s="133"/>
+      <c r="I37" s="133"/>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="131" t="s">
+      <c r="A38" s="103" t="s">
         <v>65</v>
       </c>
-      <c r="B38" s="131"/>
-      <c r="C38" s="131"/>
-      <c r="D38" s="131"/>
-      <c r="E38" s="131"/>
-      <c r="F38" s="131"/>
-      <c r="G38" s="131"/>
-      <c r="H38" s="131"/>
-      <c r="I38" s="131"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="103"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="103"/>
+      <c r="F38" s="103"/>
+      <c r="G38" s="103"/>
+      <c r="H38" s="103"/>
+      <c r="I38" s="103"/>
     </row>
     <row r="39" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="111" t="s">
+      <c r="A39" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="B39" s="112"/>
-      <c r="C39" s="112"/>
-      <c r="D39" s="112"/>
-      <c r="E39" s="112"/>
-      <c r="F39" s="112"/>
-      <c r="G39" s="112"/>
-      <c r="H39" s="112"/>
-      <c r="I39" s="113"/>
+      <c r="B39" s="92"/>
+      <c r="C39" s="92"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="92"/>
+      <c r="I39" s="93"/>
     </row>
     <row r="40" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="114"/>
-      <c r="B40" s="115"/>
-      <c r="C40" s="115"/>
-      <c r="D40" s="115"/>
-      <c r="E40" s="115"/>
-      <c r="F40" s="115"/>
-      <c r="G40" s="115"/>
-      <c r="H40" s="115"/>
-      <c r="I40" s="116"/>
+      <c r="A40" s="94"/>
+      <c r="B40" s="95"/>
+      <c r="C40" s="95"/>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="96"/>
     </row>
     <row r="41" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="114"/>
-      <c r="B41" s="115"/>
-      <c r="C41" s="115"/>
-      <c r="D41" s="115"/>
-      <c r="E41" s="115"/>
-      <c r="F41" s="115"/>
-      <c r="G41" s="115"/>
-      <c r="H41" s="115"/>
-      <c r="I41" s="116"/>
+      <c r="A41" s="94"/>
+      <c r="B41" s="95"/>
+      <c r="C41" s="95"/>
+      <c r="D41" s="95"/>
+      <c r="E41" s="95"/>
+      <c r="F41" s="95"/>
+      <c r="G41" s="95"/>
+      <c r="H41" s="95"/>
+      <c r="I41" s="96"/>
     </row>
     <row r="42" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="117"/>
-      <c r="B42" s="118"/>
-      <c r="C42" s="118"/>
-      <c r="D42" s="118"/>
-      <c r="E42" s="118"/>
-      <c r="F42" s="118"/>
-      <c r="G42" s="118"/>
-      <c r="H42" s="118"/>
-      <c r="I42" s="119"/>
+      <c r="A42" s="97"/>
+      <c r="B42" s="98"/>
+      <c r="C42" s="98"/>
+      <c r="D42" s="98"/>
+      <c r="E42" s="98"/>
+      <c r="F42" s="98"/>
+      <c r="G42" s="98"/>
+      <c r="H42" s="98"/>
+      <c r="I42" s="99"/>
     </row>
     <row r="43" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="131" t="s">
+      <c r="A43" s="103" t="s">
         <v>67</v>
       </c>
-      <c r="B43" s="131"/>
-      <c r="C43" s="131"/>
-      <c r="D43" s="131"/>
-      <c r="E43" s="131"/>
-      <c r="F43" s="131"/>
-      <c r="G43" s="131"/>
-      <c r="H43" s="131"/>
-      <c r="I43" s="131"/>
+      <c r="B43" s="103"/>
+      <c r="C43" s="103"/>
+      <c r="D43" s="103"/>
+      <c r="E43" s="103"/>
+      <c r="F43" s="103"/>
+      <c r="G43" s="103"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="103"/>
     </row>
     <row r="44" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="111" t="s">
+      <c r="A44" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="B44" s="112"/>
-      <c r="C44" s="112"/>
-      <c r="D44" s="112"/>
-      <c r="E44" s="112"/>
-      <c r="F44" s="112"/>
-      <c r="G44" s="112"/>
-      <c r="H44" s="112"/>
-      <c r="I44" s="113"/>
+      <c r="B44" s="92"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
+      <c r="F44" s="92"/>
+      <c r="G44" s="92"/>
+      <c r="H44" s="92"/>
+      <c r="I44" s="93"/>
     </row>
     <row r="45" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="114"/>
-      <c r="B45" s="115"/>
-      <c r="C45" s="115"/>
-      <c r="D45" s="115"/>
-      <c r="E45" s="115"/>
-      <c r="F45" s="115"/>
-      <c r="G45" s="115"/>
-      <c r="H45" s="115"/>
-      <c r="I45" s="116"/>
+      <c r="A45" s="94"/>
+      <c r="B45" s="95"/>
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
+      <c r="F45" s="95"/>
+      <c r="G45" s="95"/>
+      <c r="H45" s="95"/>
+      <c r="I45" s="96"/>
     </row>
     <row r="46" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="114"/>
-      <c r="B46" s="115"/>
-      <c r="C46" s="115"/>
-      <c r="D46" s="115"/>
-      <c r="E46" s="115"/>
-      <c r="F46" s="115"/>
-      <c r="G46" s="115"/>
-      <c r="H46" s="115"/>
-      <c r="I46" s="116"/>
+      <c r="A46" s="94"/>
+      <c r="B46" s="95"/>
+      <c r="C46" s="95"/>
+      <c r="D46" s="95"/>
+      <c r="E46" s="95"/>
+      <c r="F46" s="95"/>
+      <c r="G46" s="95"/>
+      <c r="H46" s="95"/>
+      <c r="I46" s="96"/>
     </row>
     <row r="47" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="117"/>
-      <c r="B47" s="118"/>
-      <c r="C47" s="118"/>
-      <c r="D47" s="118"/>
-      <c r="E47" s="118"/>
-      <c r="F47" s="118"/>
-      <c r="G47" s="118"/>
-      <c r="H47" s="118"/>
-      <c r="I47" s="119"/>
+      <c r="A47" s="97"/>
+      <c r="B47" s="98"/>
+      <c r="C47" s="98"/>
+      <c r="D47" s="98"/>
+      <c r="E47" s="98"/>
+      <c r="F47" s="98"/>
+      <c r="G47" s="98"/>
+      <c r="H47" s="98"/>
+      <c r="I47" s="99"/>
     </row>
     <row r="48" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="49" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -18234,6 +18234,25 @@
     <row r="62" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="A36:I37"/>
+    <mergeCell ref="A39:I42"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="A21:I21"/>
     <mergeCell ref="A44:I47"/>
     <mergeCell ref="K4:K6"/>
     <mergeCell ref="L4:L6"/>
@@ -18250,25 +18269,6 @@
     <mergeCell ref="A22:I23"/>
     <mergeCell ref="A24:I31"/>
     <mergeCell ref="A33:I34"/>
-    <mergeCell ref="A36:I37"/>
-    <mergeCell ref="A39:I42"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="F19:I19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:I16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="F17:I17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:I15"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -52223,7 +52223,7 @@
         <v>3347</v>
       </c>
       <c r="J221" s="56" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="K221" s="56" t="s">
         <v>3152</v>
